--- a/Practical-7thJuly.xlsx
+++ b/Practical-7thJuly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Devanshu\Desktop\Python\jupyter projects\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2213190-ED1D-4CAF-A37E-B63FC1F0D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F16800-26EE-4C56-96F0-1011CF3753F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2548,6 +2548,7 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.88671875" customWidth="1"/>
     <col min="11" max="11" width="18.6640625" customWidth="1"/>
     <col min="12" max="12" width="32" customWidth="1"/>
